--- a/data/external/soil/rakican-soil-for-aquacrop.xlsx
+++ b/data/external/soil/rakican-soil-for-aquacrop.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B8AE8F-3C4B-4085-8765-3EF9810E4C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60930" yWindow="1020" windowWidth="15975" windowHeight="18855" xr2:uid="{39A94E55-466D-48EB-B751-2B0C1B48804C}"/>
+    <workbookView xWindow="42780" yWindow="915" windowWidth="32895" windowHeight="18435" xr2:uid="{39A94E55-466D-48EB-B751-2B0C1B48804C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/external/soil/rakican-soil-for-aquacrop.xlsx
+++ b/data/external/soil/rakican-soil-for-aquacrop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rokku\Documents\Code\aquacrop-slovenia\data\external\soil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B8AE8F-3C4B-4085-8765-3EF9810E4C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC605F9C-BB3D-47D1-A883-CBA831CDE175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42780" yWindow="915" windowWidth="32895" windowHeight="18435" xr2:uid="{39A94E55-466D-48EB-B751-2B0C1B48804C}"/>
+    <workbookView xWindow="40545" yWindow="1140" windowWidth="22740" windowHeight="18435" xr2:uid="{39A94E55-466D-48EB-B751-2B0C1B48804C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,15 +71,6 @@
     <t>Horizon [cm]</t>
   </si>
   <si>
-    <t>0-20</t>
-  </si>
-  <si>
-    <t>20-30</t>
-  </si>
-  <si>
-    <t>150-230+</t>
-  </si>
-  <si>
     <t>SOIL PROPERTIES USED IN CALIBRATION OF AQUACROP</t>
   </si>
   <si>
@@ -95,10 +86,19 @@
     <t>PWP [%]</t>
   </si>
   <si>
-    <t>30-150</t>
-  </si>
-  <si>
     <t>Analysis</t>
+  </si>
+  <si>
+    <t>Ap1 0-20</t>
+  </si>
+  <si>
+    <t>Ap2 20-30</t>
+  </si>
+  <si>
+    <t>Bg 30-150</t>
+  </si>
+  <si>
+    <t>I. 150-230+</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,7 +550,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -572,21 +572,21 @@
         <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>137</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>17</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>750</v>
